--- a/estimate_license_registry.xlsx
+++ b/estimate_license_registry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Ritesh_D/License_Easygraph/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACD2EBC-72DC-D041-9D6C-B83AB1911178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CC2D8E-2CF8-1B4A-BF61-70996F5096A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13940" yWindow="1180" windowWidth="14500" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13940" yWindow="660" windowWidth="14500" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Licenses" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>License_ID</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>14:7f:ce:e0:91:d8</t>
+  </si>
+  <si>
+    <t>9640920173</t>
+  </si>
+  <si>
+    <t>14-13-33-5E-F9-6D</t>
   </si>
 </sst>
 </file>
@@ -141,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -250,11 +256,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +315,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -342,7 +363,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LicenseRegistry" displayName="LicenseRegistry" ref="A1:C3" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="License_ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Expected_token"/>
@@ -578,9 +599,15 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
       <c r="A4" s="3"/>
